--- a/Files/Helpdesk_Escalation_Ticket_Analysis.xlsx
+++ b/Files/Helpdesk_Escalation_Ticket_Analysis.xlsx
@@ -1,19 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kgurung/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEECAA4-C8D5-F449-B154-6E9C5ED894BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Ticket Log" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Escalation Analysis" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Escalation Analysis" sheetId="3" r:id="rId2"/>
+    <sheet name="Ticket Log" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,379 +40,377 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="120">
   <si>
-    <t xml:space="preserve">Helpdesk Escalation Ticket Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-directed practice project analyzing which problem types drive helpdesk escalations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This workbook simulates a helpdesk/issue-resolution ticket queue and analyzes which problem categories escalate most often, why, and how escalated tickets compare to first-line resolutions on time to resolve. It's modeled on real frontline support patterns - most tickets are resolved directly, but some require escalation because they're outside first-line scope (admin-level access, hardware replacement, vendor involvement) or point to a deeper, unresolved root cause.
+    <t>Helpdesk Escalation Ticket Analysis</t>
+  </si>
+  <si>
+    <t>Self-directed practice project analyzing which problem types drive helpdesk escalations</t>
+  </si>
+  <si>
+    <t>This workbook simulates a helpdesk/issue-resolution ticket queue and analyzes which problem categories escalate most often, why, and how escalated tickets compare to first-line resolutions on time to resolve. It's modeled on real frontline support patterns - most tickets are resolved directly, but some require escalation because they're outside first-line scope (admin-level access, hardware replacement, vendor involvement) or point to a deeper, unresolved root cause.
 Sheets:
 1. Ticket Log - 30 simulated helpdesk tickets across 6 problem categories, each marked as escalated or resolved at first line, with an escalation reason where applicable.
 2. Escalation Analysis - formulas and charts summarizing escalation rate by category, top escalation reasons, and resolution-time comparison between escalated and first-line-resolved tickets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ticket ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalated (Y/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalation Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time to Resolve (hrs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolved By</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network/WiFi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guest WiFi network down store-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor/third-party involvement needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2/ISP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handheld scanner battery not holding charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inventory app crashing on bulk barcode scan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beyond first-line troubleshooting scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account/Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate locked out after password expired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager not receiving daily reporting emails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label printer offline at receiving dock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New hire access request needs elevated system permissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required admin-level access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitor at service desk showing no display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device dropping WiFi connection intermittently</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS terminal freezing during checkout, third occurrence this month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repeat issue - root cause unresolved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barcode scanner not reading damaged labels consistently</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate email flagged for suspicious login attempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two printers conflicting, jobs routing to wrong device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPN connection dropping for remote employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Replacement laptop needed after liquid damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardware replacement needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate unable to access shared drive after dept. transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reporting dashboard showing outdated numbers, nightly job stalled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt printer printing garbled text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access point needs replacement, third outage this month at same location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter rule misrouting sender domain to spam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docking station not charging laptop reliably</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reporting tool license expired, needs procurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procurement/Vendor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager needs temporary elevated access for month-end reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Print spooler stalled, jobs stuck in queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Router restart resolved intermittent drops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tablet used for curbside pickup not charging, cable failure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project tracking tool not syncing across team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same associate locked out for the second time this week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mailbox over storage limit, bulk archive needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCK-3030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application requires vendor patch for known bug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalation Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolled up from the Ticket Log (practice data).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Tickets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escalation Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Tickets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Escalated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Escalation Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Time to Resolve - Escalated (hrs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Time to Resolve - First-Line (hrs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category with Highest Escalation Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reading this report: categories with a high escalation rate (Hardware, Software) tend to need physical replacement or vendor/engineering involvement that first-line support can't resolve alone. Categories with a low escalation rate (Printer, Email) are mostly resolved with a standard first-line fix. Repeat escalations ("root cause unresolved") point to issues worth flagging for a permanent fix rather than re-solving the same ticket every time.</t>
+    <t>Ticket ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Problem Description</t>
+  </si>
+  <si>
+    <t>Escalated (Y/N)</t>
+  </si>
+  <si>
+    <t>Escalation Reason</t>
+  </si>
+  <si>
+    <t>Time to Resolve (hrs)</t>
+  </si>
+  <si>
+    <t>Resolved By</t>
+  </si>
+  <si>
+    <t>TCK-3001</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>Network/WiFi</t>
+  </si>
+  <si>
+    <t>Guest WiFi network down store-wide</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Vendor/third-party involvement needed</t>
+  </si>
+  <si>
+    <t>Tier 2/ISP</t>
+  </si>
+  <si>
+    <t>TCK-3002</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Handheld scanner battery not holding charge</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Tier 1</t>
+  </si>
+  <si>
+    <t>TCK-3003</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Inventory app crashing on bulk barcode scan</t>
+  </si>
+  <si>
+    <t>Beyond first-line troubleshooting scope</t>
+  </si>
+  <si>
+    <t>App Support</t>
+  </si>
+  <si>
+    <t>TCK-3004</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>Account/Access</t>
+  </si>
+  <si>
+    <t>Associate locked out after password expired</t>
+  </si>
+  <si>
+    <t>TCK-3005</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Manager not receiving daily reporting emails</t>
+  </si>
+  <si>
+    <t>TCK-3006</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Label printer offline at receiving dock</t>
+  </si>
+  <si>
+    <t>TCK-3007</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>New hire access request needs elevated system permissions</t>
+  </si>
+  <si>
+    <t>Required admin-level access</t>
+  </si>
+  <si>
+    <t>IT Admin</t>
+  </si>
+  <si>
+    <t>TCK-3008</t>
+  </si>
+  <si>
+    <t>Monitor at service desk showing no display</t>
+  </si>
+  <si>
+    <t>TCK-3009</t>
+  </si>
+  <si>
+    <t>Device dropping WiFi connection intermittently</t>
+  </si>
+  <si>
+    <t>TCK-3010</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>POS terminal freezing during checkout, third occurrence this month</t>
+  </si>
+  <si>
+    <t>Repeat issue - root cause unresolved</t>
+  </si>
+  <si>
+    <t>TCK-3011</t>
+  </si>
+  <si>
+    <t>Barcode scanner not reading damaged labels consistently</t>
+  </si>
+  <si>
+    <t>TCK-3012</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>Associate email flagged for suspicious login attempt</t>
+  </si>
+  <si>
+    <t>Security Team</t>
+  </si>
+  <si>
+    <t>TCK-3013</t>
+  </si>
+  <si>
+    <t>Two printers conflicting, jobs routing to wrong device</t>
+  </si>
+  <si>
+    <t>TCK-3014</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>VPN connection dropping for remote employee</t>
+  </si>
+  <si>
+    <t>TCK-3015</t>
+  </si>
+  <si>
+    <t>Replacement laptop needed after liquid damage</t>
+  </si>
+  <si>
+    <t>Hardware replacement needed</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>TCK-3016</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>Associate unable to access shared drive after dept. transfer</t>
+  </si>
+  <si>
+    <t>TCK-3017</t>
+  </si>
+  <si>
+    <t>Reporting dashboard showing outdated numbers, nightly job stalled</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>TCK-3018</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>Receipt printer printing garbled text</t>
+  </si>
+  <si>
+    <t>TCK-3019</t>
+  </si>
+  <si>
+    <t>Access point needs replacement, third outage this month at same location</t>
+  </si>
+  <si>
+    <t>Facilities</t>
+  </si>
+  <si>
+    <t>TCK-3020</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Filter rule misrouting sender domain to spam</t>
+  </si>
+  <si>
+    <t>TCK-3021</t>
+  </si>
+  <si>
+    <t>Docking station not charging laptop reliably</t>
+  </si>
+  <si>
+    <t>TCK-3022</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Reporting tool license expired, needs procurement</t>
+  </si>
+  <si>
+    <t>Procurement/Vendor</t>
+  </si>
+  <si>
+    <t>TCK-3023</t>
+  </si>
+  <si>
+    <t>Manager needs temporary elevated access for month-end reporting</t>
+  </si>
+  <si>
+    <t>TCK-3024</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>Print spooler stalled, jobs stuck in queue</t>
+  </si>
+  <si>
+    <t>TCK-3025</t>
+  </si>
+  <si>
+    <t>Router restart resolved intermittent drops</t>
+  </si>
+  <si>
+    <t>TCK-3026</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>Tablet used for curbside pickup not charging, cable failure</t>
+  </si>
+  <si>
+    <t>TCK-3027</t>
+  </si>
+  <si>
+    <t>Project tracking tool not syncing across team</t>
+  </si>
+  <si>
+    <t>TCK-3028</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Same associate locked out for the second time this week</t>
+  </si>
+  <si>
+    <t>TCK-3029</t>
+  </si>
+  <si>
+    <t>Mailbox over storage limit, bulk archive needed</t>
+  </si>
+  <si>
+    <t>TCK-3030</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>Application requires vendor patch for known bug</t>
+  </si>
+  <si>
+    <t>Vendor Support</t>
+  </si>
+  <si>
+    <t>Escalation Analysis</t>
+  </si>
+  <si>
+    <t>Rolled up from the Ticket Log (practice data).</t>
+  </si>
+  <si>
+    <t>Total Tickets</t>
+  </si>
+  <si>
+    <t>Escalated</t>
+  </si>
+  <si>
+    <t>Escalation Rate</t>
+  </si>
+  <si>
+    <t># Tickets</t>
+  </si>
+  <si>
+    <t>Total Escalated</t>
+  </si>
+  <si>
+    <t>Overall Escalation Rate</t>
+  </si>
+  <si>
+    <t>Avg Time to Resolve - Escalated (hrs)</t>
+  </si>
+  <si>
+    <t>Avg Time to Resolve - First-Line (hrs)</t>
+  </si>
+  <si>
+    <t>Category with Highest Escalation Rate</t>
+  </si>
+  <si>
+    <t>Reading this report: categories with a high escalation rate (Hardware, Software) tend to need physical replacement or vendor/engineering involvement that first-line support can't resolve alone. Categories with a low escalation rate (Printer, Email) are mostly resolved with a standard first-line fix. Repeat escalations ("root cause unresolved") point to issues worth flagging for a permanent fix rather than re-solving the same ticket every time.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,91 +419,49 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
+      <color rgb="FF555555"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -508,14 +480,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -524,7 +496,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -540,142 +512,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Report Header" xfId="20"/>
+    <cellStyle name="Report Header" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6DADA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF222222"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF3B0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -684,6 +559,7 @@
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -742,15 +618,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF222222"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -759,7 +653,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -767,7 +661,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -788,6 +682,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -797,7 +692,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Escalation Analysis'!D4</c:f>
+              <c:f>'Escalation Analysis'!$D$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -808,7 +703,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -816,15 +711,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -832,8 +735,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -876,10 +780,10 @@
                   <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.167</c:v>
+                  <c:v>0.16700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.833</c:v>
+                  <c:v>0.83299999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.6</c:v>
@@ -893,9 +797,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-ED15-A74B-A8DD-27371B3ED6F2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="85361361"/>
         <c:axId val="7737369"/>
       </c:barChart>
@@ -913,7 +829,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -921,7 +837,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -957,13 +873,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="7737369"/>
@@ -997,7 +914,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1005,7 +922,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1041,13 +958,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="85361361"/>
@@ -1075,37 +993,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1114,7 +1041,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1122,7 +1049,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1143,6 +1070,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -1150,7 +1078,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Escalation Analysis'!B13</c:f>
+              <c:f>'Escalation Analysis'!$B$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1161,80 +1089,103 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:explosion val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7C9C-2340-955B-5640C279EBBB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4f81bd"/>
+                <a:srgbClr val="C0504D"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7C9C-2340-955B-5640C279EBBB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
-            <c:idx val="1"/>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="c0504d"/>
+                <a:srgbClr val="9BBB59"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7C9C-2340-955B-5640C279EBBB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
-            <c:idx val="2"/>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="9bbb59"/>
+                <a:srgbClr val="8064A2"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-7C9C-2340-955B-5640C279EBBB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
-            <c:idx val="3"/>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="8064a2"/>
+                <a:srgbClr val="4BACC6"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4bacc6"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-7C9C-2340-955B-5640C279EBBB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
@@ -1242,19 +1193,27 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-7C9C-2340-955B-5640C279EBBB}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
@@ -1262,19 +1221,27 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-7C9C-2340-955B-5640C279EBBB}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
@@ -1282,19 +1249,27 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-7C9C-2340-955B-5640C279EBBB}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
@@ -1302,19 +1277,27 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-7C9C-2340-955B-5640C279EBBB}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
@@ -1322,17 +1305,31 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-7C9C-2340-955B-5640C279EBBB}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1340,8 +1337,12 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1390,7 +1391,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-7C9C-2340-955B-5640C279EBBB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
       <c:spPr>
@@ -1414,35 +1429,42 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1456,14 +1478,20 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>28800</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5545440" y="571680"/>
-        <a:ext cx="5039640" cy="2519640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1486,14 +1514,20 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>28440</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5545440" y="3619440"/>
-        <a:ext cx="5039640" cy="2519640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1507,57 +1541,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TicketLog" displayName="TicketLog" ref="A1:H31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TicketLog" displayName="TicketLog" ref="A1:H31" totalsRowShown="0">
+  <autoFilter ref="A1:H31" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Ticket ID"/>
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="Category"/>
-    <tableColumn id="4" name="Problem Description"/>
-    <tableColumn id="5" name="Escalated (Y/N)"/>
-    <tableColumn id="6" name="Escalation Reason"/>
-    <tableColumn id="7" name="Time to Resolve (hrs)"/>
-    <tableColumn id="8" name="Resolved By"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ticket ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Problem Description"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Escalated (Y/N)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Escalation Reason"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Time to Resolve (hrs)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Resolved By"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1565,12 +1600,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1599,7 +1634,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1620,7 +1655,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1671,7 +1706,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1689,134 +1724,133 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="14"/>
+    <col min="1" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="189.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="4" spans="1:6" ht="189.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1824,815 +1858,1104 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F14"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A5)</f>
+        <v>5</v>
+      </c>
+      <c r="C5" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A5,'Ticket Log'!E2:E31,"Y")</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5:D10" si="0">IFERROR(ROUND(C5/B5,3),0)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A6)</f>
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A6,'Ticket Log'!E2:E31,"Y")</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A7)</f>
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A7,'Ticket Log'!E2:E31,"Y")</f>
+        <v>5</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>0.83299999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A8)</f>
+        <v>5</v>
+      </c>
+      <c r="C8" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A8,'Ticket Log'!E2:E31,"Y")</f>
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A9)</f>
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C9" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A9,'Ticket Log'!E2:E31,"Y")</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A10)</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <f>COUNTIFS('Ticket Log'!C2:C31,A10,'Ticket Log'!E2:E31,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="5">
+        <f>COUNTIF('Ticket Log'!F2:F31,A14)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="5">
+        <f>COUNTIF('Ticket Log'!F2:F31,A15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5">
+        <f>COUNTIF('Ticket Log'!F2:F31,A16)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="5">
+        <f>COUNTIF('Ticket Log'!F2:F31,A17)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="5">
+        <f>COUNTIF('Ticket Log'!F2:F31,A18)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="8">
+        <f>COUNTA('Ticket Log'!A2:A31)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="8">
+        <f>COUNTIF('Ticket Log'!E2:E31,"Y")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="9">
+        <f>ROUND(B22/B21,3)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="8">
+        <f>ROUND(AVERAGEIFS('Ticket Log'!G2:G31,'Ticket Log'!E2:E31,"Y"),2)</f>
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="8">
+        <f>ROUND(AVERAGEIFS('Ticket Log'!G2:G31,'Ticket Log'!E2:E31,"N"),2)</f>
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="8" t="str">
+        <f>INDEX(A5:A10,MATCH(MAX(D5:D10),D5:D10,0))</f>
+        <v>Software</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D31"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D10">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFC6E8C6"/>
+        <color rgb="FFF4C7C3"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="2">
         <v>3.5</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="n">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2">
         <v>0.4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="2">
         <v>2</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
         <v>0.25</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="n">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
         <v>0.6</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
         <v>0.5</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
         <v>0.3</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="n">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
         <v>0.5</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="2">
         <v>1.5</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="n">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
         <v>0.4</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="2">
         <v>0.9</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="n">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2">
         <v>0.7</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5" t="n">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2">
         <v>0.6</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="2">
         <v>4</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5" t="n">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2">
         <v>0.5</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="2">
         <v>1.3</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5" t="n">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2">
         <v>0.4</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="2">
         <v>3</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="n">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2">
         <v>0.5</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5" t="n">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2">
         <v>0.35</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="2">
         <v>2.5</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="2">
         <v>0.5</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5" t="n">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2">
         <v>0.3</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5" t="n">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
         <v>0.4</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5" t="n">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2">
         <v>0.3</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5" t="n">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2">
         <v>0.8</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="2">
         <v>0.6</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5" t="n">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2">
         <v>0.5</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="2">
         <v>3</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="2" t="s">
         <v>107</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E31">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G31">
     <cfRule type="dataBar" priority="3">
-      <dataBar showValue="1" minLength="10" maxLength="90">
-        <cfvo type="min" val="0"/>
-        <cfvo type="max" val="0"/>
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
         <color rgb="FF6FA8DC"/>
       </dataBar>
       <extLst>
@@ -2642,14 +2965,9 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
   <extLst>
@@ -2657,11 +2975,10 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{642084EF-779F-4CAD-A718-C022ACE9C265}">
-            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+            <x14:dataBar axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:negativeFillColor rgb="FF6FA8DC"/>
-              <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>G2:G31</xm:sqref>
@@ -2670,309 +2987,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A5)</f>
-        <v>5</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A5,'Ticket Log'!E2:E31,"Y")</f>
-        <v>2</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C5/B5,3),0)</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A6)</f>
-        <v>6</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A6,'Ticket Log'!E2:E31,"Y")</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C6/B6,3),0)</f>
-        <v>0.167</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A7)</f>
-        <v>6</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A7,'Ticket Log'!E2:E31,"Y")</f>
-        <v>5</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C7/B7,3),0)</f>
-        <v>0.833</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A8)</f>
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A8,'Ticket Log'!E2:E31,"Y")</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C8/B8,3),0)</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A9)</f>
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A9,'Ticket Log'!E2:E31,"Y")</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C9/B9,3),0)</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A10)</f>
-        <v>4</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <f aca="false">COUNTIFS('Ticket Log'!C2:C31,A10,'Ticket Log'!E2:E31,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <f aca="false">IFERROR(ROUND(C10/B10,3),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!F2:F31,A14)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!F2:F31,A15)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!F2:F31,A16)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="10" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!F2:F31,A17)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="10" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!F2:F31,A18)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="13" t="n">
-        <f aca="false">COUNTA('Ticket Log'!A2:A31)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="13" t="n">
-        <f aca="false">COUNTIF('Ticket Log'!E2:E31,"Y")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <f aca="false">ROUND(B22/B21,3)</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" s="13" t="n">
-        <f aca="false">ROUND(AVERAGEIFS('Ticket Log'!G2:G31,'Ticket Log'!E2:E31,"Y"),2)</f>
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="13" t="n">
-        <f aca="false">ROUND(AVERAGEIFS('Ticket Log'!G2:G31,'Ticket Log'!E2:E31,"N"),2)</f>
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="13" t="str">
-        <f aca="false">INDEX(A5:A10,MATCH(MAX(D5:D10),D5:D10,0))</f>
-        <v>Software</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A28:D31"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D5:D10">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6E8C6"/>
-        <color rgb="FFF4C7C3"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>